--- a/uploads/excel/Student_2022_two.xlsx
+++ b/uploads/excel/Student_2022_two.xlsx
@@ -44,9 +44,6 @@
     <t>nationality</t>
   </si>
   <si>
-    <t>nid</t>
-  </si>
-  <si>
     <t>present_address</t>
   </si>
   <si>
@@ -62,39 +59,18 @@
     <t>class_id</t>
   </si>
   <si>
-    <t>student_email</t>
-  </si>
-  <si>
-    <t>father_email</t>
-  </si>
-  <si>
-    <t>mother_email</t>
-  </si>
-  <si>
-    <t>guardian_email</t>
-  </si>
-  <si>
     <t>father_mobile</t>
   </si>
   <si>
     <t>mother_mobile</t>
   </si>
   <si>
-    <t>signature</t>
-  </si>
-  <si>
     <t>guardian_name</t>
   </si>
   <si>
     <t>guardian_profession</t>
   </si>
   <si>
-    <t>guardian_organization</t>
-  </si>
-  <si>
-    <t>guardian_relation</t>
-  </si>
-  <si>
     <t>guardian_mobile</t>
   </si>
   <si>
@@ -116,19 +92,22 @@
     <t>Male</t>
   </si>
   <si>
-    <t>0000-00-00</t>
+    <t>2026-06-29</t>
   </si>
   <si>
     <t>O+</t>
   </si>
   <si>
+    <t>Hinduism</t>
+  </si>
+  <si>
     <t>bd</t>
   </si>
   <si>
-    <t>gfdsgdfsdfg</t>
-  </si>
-  <si>
-    <t>dfsg</t>
+    <t>df</t>
+  </si>
+  <si>
+    <t>gfd</t>
   </si>
   <si>
     <t>ry</t>
@@ -137,10 +116,31 @@
     <t>rt</t>
   </si>
   <si>
-    <t>../uploads/students/2021-one/Md-Ratan-Ali.jpg</t>
-  </si>
-  <si>
-    <t>2026-02-10 00:49:52</t>
+    <t>2026-06-29 08:05:50</t>
+  </si>
+  <si>
+    <t>Md Raj</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>gfh</t>
+  </si>
+  <si>
+    <t>gfhd</t>
+  </si>
+  <si>
+    <t>try</t>
+  </si>
+  <si>
+    <t>ryt</t>
+  </si>
+  <si>
+    <t>uploads/students/2021-one/2-Md-Raj/Md-Raj.jpg</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:50:48</t>
   </si>
 </sst>
 </file>
@@ -480,10 +480,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,93 +550,131 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="E2" t="s">
         <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
       </c>
       <c r="F2">
         <v>345</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>2</v>
       </c>
       <c r="O2">
+        <v>536</v>
+      </c>
+      <c r="P2">
+        <v>534</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3">
+        <v>345</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="T2">
-        <v>536</v>
-      </c>
-      <c r="U2">
-        <v>3456</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>56</v>
+      </c>
+      <c r="P3">
+        <v>456</v>
+      </c>
+      <c r="Q3" t="s">
         <v>38</v>
       </c>
-      <c r="X2" t="s">
+      <c r="R3" t="s">
         <v>39</v>
       </c>
-      <c r="AA2">
-        <v>54</v>
-      </c>
-      <c r="AC2" t="s">
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U3" t="s">
         <v>40</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="V3" t="s">
         <v>41</v>
       </c>
     </row>
